--- a/output/pdf_financials_xlsx/GLAD.xlsx
+++ b/output/pdf_financials_xlsx/GLAD.xlsx
@@ -6168,49 +6168,49 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.051904</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.051904</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.051904</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.101904</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.101904</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.101904</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.101904</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.101904</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.101904</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.101904</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.379372</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.5652470000000001</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.672116</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.877506</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.545942</v>
       </c>
     </row>
     <row r="93">
@@ -10414,7 +10414,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11404,7 +11408,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -12616,7 +12624,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -13200,7 +13212,11 @@
           <t>Reserves (note 5)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -13687,7 +13703,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -14190,7 +14210,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -14584,7 +14608,11 @@
           <t>Reserves (note 5)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GLAD.xlsx
+++ b/output/pdf_financials_xlsx/GLAD.xlsx
@@ -1101,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000794</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002076</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2149,10 +2149,10 @@
         <v>-0.006032</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.093303</v>
+        <v>-0.094097</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.051232</v>
+        <v>-0.053308</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.187055</v>
@@ -2281,10 +2281,10 @@
         <v>-0.006032</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.093303</v>
+        <v>-0.094097</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.051232</v>
+        <v>-0.053308</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.187055</v>
@@ -2608,28 +2608,28 @@
         <v>0.165629</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.097068</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.058247</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003616</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.04282</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.014965</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.045095</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.01909</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.313674</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1.957683</v>
@@ -2724,28 +2724,28 @@
         <v>0.165629</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.097068</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.058247</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003616</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.04282</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.014965</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.045095</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.01909</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.313674</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1.957683</v>
@@ -3420,28 +3420,28 @@
         <v>0.029795</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.097068</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.058664</v>
+        <v>0.000417</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.005096</v>
+        <v>0.00148</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.043702</v>
+        <v>0.000882</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.015382</v>
+        <v>0.000417</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.045512</v>
+        <v>0.000417</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.020052</v>
+        <v>0.000962</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.314091</v>
+        <v>0.000417</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.001667</v>
@@ -11810,7 +11810,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -12319,7 +12323,11 @@
           <t>Reclamation deposit 5</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -12830,7 +12838,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -36008,7 +36016,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -36521,7 +36529,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -37036,7 +37044,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
